--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,8 +779,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90000964</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 1520-2022 artfynd.xlsx
+++ b/artfynd/A 1520-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,9 +785,255 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136484347</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57917</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sångbäckvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>455383</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6927705</v>
+      </c>
+      <c r="S3" t="n">
+        <v>7</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>uhlie Evertsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>uhlie Evertsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136484347</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136484349</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58665</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103046</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gråsiska</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Acanthis flammea</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sångbäckvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>455383</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6927705</v>
+      </c>
+      <c r="S4" t="n">
+        <v>7</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Berg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Klövsjö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>uhlie Evertsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>uhlie Evertsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136484349</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
